--- a/tests/TC-15/results/teacher_timetables_even.xlsx
+++ b/tests/TC-15/results/teacher_timetables_even.xlsx
@@ -626,21 +626,21 @@
         <is>
           <t>CS1 TUT
 (CSE_4_B)
-Room: 109</t>
+Room: 106</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>CS1 TUT
 (CSE_4_B)
-Room: 109</t>
+Room: 106</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>CS1 TUT
 (CSE_4_B)
-Room: 109</t>
+Room: 106</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
@@ -666,34 +666,10 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
@@ -703,9 +679,27 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -753,24 +747,30 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>CS1 LEC
 (CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>CS1 LEC
 (CSE_4_B)
-Room: 105</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -963,8 +963,20 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1028,13 +1040,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS2 TUT
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1054,34 +1060,10 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -1091,7 +1073,13 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>CS2 TUT
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
@@ -1103,35 +1091,35 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>CS2 LEC
 (CSE_4_B)
-Room: 107</t>
+Room: 110</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>CS2 LEC
 (CSE_4_B)
-Room: 107</t>
+Room: 110</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>CS2 LEC
 (CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+Room: 110</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1306,13 +1294,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>CS3 TUT
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
@@ -1323,9 +1305,27 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1349,20 +1349,8 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1380,37 +1368,25 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>CS3 TUT
 (CSE_4_B)
 Room: 110</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>CS3 TUT
 (CSE_4_B)
 Room: 110</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1430,10 +1406,34 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1654,13 +1654,7 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>CS4 TUT
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -1673,10 +1667,34 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -1710,27 +1728,9 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -1742,27 +1742,27 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>CS4 TUT
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>CS4 TUT
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1792,9 +1792,27 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
@@ -1989,7 +2007,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CS5 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
@@ -2003,27 +2027,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -2044,20 +2050,26 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>CS5 TUT
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -2077,30 +2089,24 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>

--- a/tests/TC-15/results/teacher_timetables_even.xlsx
+++ b/tests/TC-15/results/teacher_timetables_even.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,10 +99,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -622,27 +622,9 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS1 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS1 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS1 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -659,49 +641,49 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>CS1 LEC
 (CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
+Room: 103</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>CS1 LEC
 (CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
+Room: 103</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>CS1 LEC
 (CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+Room: 103</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -714,10 +696,34 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>CS1 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
@@ -731,49 +737,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>CS1 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -787,9 +775,27 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS1 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CS1 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CS1 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -963,26 +969,38 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
@@ -996,31 +1014,55 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>CS2 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1050,37 +1092,37 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>CS2 TUT
 (CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
+Room: 105</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1091,34 +1133,10 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>CS2 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
@@ -1305,25 +1323,25 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>CS3 LEC
 (CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>CS3 LEC
 (CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>CS3 LEC
 (CSE_4_B)
-Room: 101</t>
+Room: 102</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1333,31 +1351,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1373,23 +1391,23 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>CS3 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>CS3 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>CS3 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1399,55 +1417,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>CS3 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1467,7 +1461,13 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS3 TUT
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -1658,55 +1658,43 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>CS4 LEC
 (CSE_4_B)
 Room: 103</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>CS4 LEC
 (CSE_4_B)
 Room: 103</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1728,51 +1716,57 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>CS4 LEC
+(CSE_4_B)
+Room: 103</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>CS4 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>CS4 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1792,31 +1786,19 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>CS4 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>CS4 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1995,43 +1977,49 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>CS5 TUT
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>CS5 TUT
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>CS5 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2040,8 +2028,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -2050,20 +2050,8 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -2073,43 +2061,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>CS5 LEC
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2131,9 +2107,27 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>CS5 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
